--- a/analysis/comparison_table.xlsx
+++ b/analysis/comparison_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,35 +446,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Modo Chunk</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Recall@10</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>MRR@10</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nDCG@10</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Rendimiento (media 3 métricas)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>QPS</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ahorro Storage (%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Factor Compresión (×)</t>
         </is>
@@ -483,37 +488,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SBERT-384</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SBERT</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>384</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.917</v>
+        <v>192</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>0.727</v>
+        <v>0.899</v>
       </c>
       <c r="F2" t="n">
-        <v>0.773</v>
+        <v>0.696</v>
       </c>
       <c r="G2" t="n">
-        <v>0.806</v>
+        <v>0.746</v>
       </c>
       <c r="H2" t="n">
-        <v>30043.616</v>
+        <v>0.78</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>29445.998</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -530,246 +540,283 @@
       <c r="C3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.888</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E3" t="n">
-        <v>0.676</v>
+        <v>0.897</v>
       </c>
       <c r="F3" t="n">
-        <v>0.728</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.764</v>
+        <v>0.741</v>
       </c>
       <c r="H3" t="n">
-        <v>62462.439</v>
+        <v>0.776</v>
       </c>
       <c r="I3" t="n">
+        <v>29637.765</v>
+      </c>
+      <c r="J3" t="n">
         <v>50</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>CAE-lat160</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>128</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.886</v>
+        <v>160</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E4" t="n">
-        <v>0.668</v>
+        <v>0.895</v>
       </c>
       <c r="F4" t="n">
-        <v>0.721</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.758</v>
+        <v>0.74</v>
       </c>
       <c r="H4" t="n">
-        <v>83129.515</v>
+        <v>0.775</v>
       </c>
       <c r="I4" t="n">
-        <v>66.7</v>
+        <v>31583.961</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>58.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CAE-lat160</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>160</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.88</v>
+        <v>128</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E5" t="n">
-        <v>0.664</v>
+        <v>0.893</v>
       </c>
       <c r="F5" t="n">
-        <v>0.716</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.753</v>
+        <v>0.74</v>
       </c>
       <c r="H5" t="n">
-        <v>71530.22500000001</v>
+        <v>0.775</v>
       </c>
       <c r="I5" t="n">
-        <v>58.3</v>
+        <v>42652.006</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4</v>
+        <v>66.7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BM25</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BM25</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>384</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.829</v>
+        <v>128</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E6" t="n">
-        <v>0.679</v>
+        <v>0.893</v>
       </c>
       <c r="F6" t="n">
-        <v>0.715</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>0.736</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.771</v>
+      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>44565.48</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>66.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>CAE-lat160</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>96</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.862</v>
+        <v>160</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E7" t="n">
-        <v>0.639</v>
+        <v>0.889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.731</v>
+        <v>0.733</v>
       </c>
       <c r="H7" t="n">
-        <v>105215.94</v>
+        <v>0.768</v>
       </c>
       <c r="I7" t="n">
-        <v>75</v>
+        <v>33692.215</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>58.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DAE-lat192</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DAE</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>192</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.862</v>
+        <v>96</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E8" t="n">
-        <v>0.628</v>
+        <v>0.877</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.668</v>
       </c>
       <c r="G8" t="n">
-        <v>0.725</v>
+        <v>0.718</v>
       </c>
       <c r="H8" t="n">
-        <v>60888.765</v>
+        <v>0.754</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>50565.486</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DAE-lat128</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DAE</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>128</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.858</v>
+        <v>96</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E9" t="n">
-        <v>0.624</v>
+        <v>0.877</v>
       </c>
       <c r="F9" t="n">
-        <v>0.681</v>
+        <v>0.66</v>
       </c>
       <c r="G9" t="n">
-        <v>0.721</v>
+        <v>0.712</v>
       </c>
       <c r="H9" t="n">
-        <v>84828.209</v>
+        <v>0.75</v>
       </c>
       <c r="I9" t="n">
-        <v>66.7</v>
+        <v>53720.031</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DAE-lat96</t>
+          <t>DAE-lat192</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -778,142 +825,162 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>96</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.856</v>
+        <v>192</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E10" t="n">
-        <v>0.619</v>
+        <v>0.874</v>
       </c>
       <c r="F10" t="n">
-        <v>0.676</v>
+        <v>0.653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.717</v>
+        <v>0.706</v>
       </c>
       <c r="H10" t="n">
-        <v>116829.144</v>
+        <v>0.744</v>
       </c>
       <c r="I10" t="n">
-        <v>75</v>
+        <v>27046.178</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>DAE-lat128</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>DAE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.838</v>
+        <v>128</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E11" t="n">
-        <v>0.592</v>
+        <v>0.871</v>
       </c>
       <c r="F11" t="n">
-        <v>0.652</v>
+        <v>0.65</v>
       </c>
       <c r="G11" t="n">
-        <v>0.694</v>
+        <v>0.703</v>
       </c>
       <c r="H11" t="n">
-        <v>141722.109</v>
+        <v>0.741</v>
       </c>
       <c r="I11" t="n">
-        <v>83.3</v>
+        <v>36234.569</v>
       </c>
       <c r="J11" t="n">
-        <v>6</v>
+        <v>66.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CAE-lat96</t>
+          <t>DAE-lat192</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>DAE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.823</v>
+        <v>192</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E12" t="n">
-        <v>0.586</v>
+        <v>0.87</v>
       </c>
       <c r="F12" t="n">
-        <v>0.643</v>
+        <v>0.644</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.699</v>
       </c>
       <c r="H12" t="n">
-        <v>113431.611</v>
+        <v>0.738</v>
       </c>
       <c r="I12" t="n">
-        <v>75</v>
+        <v>27590.335</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CAE-lat224</t>
+          <t>DAE-lat128</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>DAE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>224</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.8149999999999999</v>
+        <v>128</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E13" t="n">
-        <v>0.579</v>
+        <v>0.867</v>
       </c>
       <c r="F13" t="n">
-        <v>0.636</v>
+        <v>0.642</v>
       </c>
       <c r="G13" t="n">
-        <v>0.677</v>
+        <v>0.696</v>
       </c>
       <c r="H13" t="n">
-        <v>52681.96</v>
+        <v>0.735</v>
       </c>
       <c r="I13" t="n">
-        <v>41.7</v>
+        <v>37323.658</v>
       </c>
       <c r="J13" t="n">
-        <v>1.71</v>
+        <v>66.7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAE-lat64</t>
+          <t>DAE-lat96</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -922,178 +989,203 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.8129999999999999</v>
+        <v>96</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.863</v>
       </c>
       <c r="F14" t="n">
-        <v>0.621</v>
+        <v>0.642</v>
       </c>
       <c r="G14" t="n">
-        <v>0.665</v>
+        <v>0.696</v>
       </c>
       <c r="H14" t="n">
-        <v>143347.903</v>
+        <v>0.734</v>
       </c>
       <c r="I14" t="n">
-        <v>83.3</v>
+        <v>47966.781</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>75</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>DAE-lat96</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>DAE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>224</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.804</v>
+        <v>96</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E15" t="n">
-        <v>0.555</v>
+        <v>0.862</v>
       </c>
       <c r="F15" t="n">
-        <v>0.615</v>
+        <v>0.634</v>
       </c>
       <c r="G15" t="n">
-        <v>0.658</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>52789.097</v>
+        <v>0.728</v>
       </c>
       <c r="I15" t="n">
-        <v>41.7</v>
+        <v>48657.959</v>
       </c>
       <c r="J15" t="n">
-        <v>1.71</v>
+        <v>75</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>CAE-lat96</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>160</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.789</v>
+        <v>96</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E16" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="F16" t="n">
-        <v>0.614</v>
+        <v>0.619</v>
       </c>
       <c r="G16" t="n">
-        <v>0.654</v>
+        <v>0.672</v>
       </c>
       <c r="H16" t="n">
-        <v>70642.065</v>
+        <v>0.711</v>
       </c>
       <c r="I16" t="n">
-        <v>58.3</v>
+        <v>47882.165</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4</v>
+        <v>75</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CAE-lat192</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>192</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.78</v>
+        <v>64</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E17" t="n">
-        <v>0.528</v>
+        <v>0.846</v>
       </c>
       <c r="F17" t="n">
-        <v>0.588</v>
+        <v>0.615</v>
       </c>
       <c r="G17" t="n">
-        <v>0.632</v>
+        <v>0.671</v>
       </c>
       <c r="H17" t="n">
-        <v>55473.616</v>
+        <v>0.711</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>66834.488</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>83.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>VAE-lat192</t>
+          <t>CAE-lat96</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VAE</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>192</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.782</v>
+        <v>96</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E18" t="n">
-        <v>0.515</v>
+        <v>0.833</v>
       </c>
       <c r="F18" t="n">
-        <v>0.579</v>
+        <v>0.612</v>
       </c>
       <c r="G18" t="n">
-        <v>0.625</v>
+        <v>0.665</v>
       </c>
       <c r="H18" t="n">
-        <v>57773.832</v>
+        <v>0.703</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>48293.501</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>75</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CAE-lat64</t>
+          <t>CAE-lat224</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1102,28 +1194,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>64</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.769</v>
+        <v>224</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E19" t="n">
-        <v>0.517</v>
+        <v>0.832</v>
       </c>
       <c r="F19" t="n">
-        <v>0.578</v>
+        <v>0.61</v>
       </c>
       <c r="G19" t="n">
-        <v>0.621</v>
+        <v>0.664</v>
       </c>
       <c r="H19" t="n">
-        <v>150669.257</v>
+        <v>0.702</v>
       </c>
       <c r="I19" t="n">
-        <v>83.3</v>
+        <v>24004.553</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>41.7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="20">
@@ -1138,205 +1235,975 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.76</v>
+        <v>64</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E20" t="n">
-        <v>0.491</v>
+        <v>0.844</v>
       </c>
       <c r="F20" t="n">
-        <v>0.555</v>
+        <v>0.606</v>
       </c>
       <c r="G20" t="n">
-        <v>0.602</v>
+        <v>0.663</v>
       </c>
       <c r="H20" t="n">
-        <v>185856.49</v>
+        <v>0.704</v>
       </c>
       <c r="I20" t="n">
-        <v>91.7</v>
+        <v>70683.66899999999</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>83.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DPR</t>
+          <t>CAE-lat224</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DPR</t>
+          <t>CAE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>384</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.74</v>
+        <v>224</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E21" t="n">
-        <v>0.483</v>
+        <v>0.827</v>
       </c>
       <c r="F21" t="n">
-        <v>0.545</v>
+        <v>0.601</v>
       </c>
       <c r="G21" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>0.656</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.695</v>
+      </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>24481.837</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>41.7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>VAE-lat160</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>VAE</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>160</v>
       </c>
-      <c r="D22" t="n">
-        <v>0.751</v>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E22" t="n">
-        <v>0.473</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.539</v>
+        <v>0.594</v>
       </c>
       <c r="G22" t="n">
-        <v>0.588</v>
+        <v>0.646</v>
       </c>
       <c r="H22" t="n">
-        <v>68376.427</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I22" t="n">
+        <v>32586.257</v>
+      </c>
+      <c r="J22" t="n">
         <v>58.3</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>2.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>VAE-lat224</t>
+          <t>DAE-lat64</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VAE</t>
+          <t>DAE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>224</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.739</v>
+        <v>64</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
       </c>
       <c r="E23" t="n">
-        <v>0.468</v>
+        <v>0.826</v>
       </c>
       <c r="F23" t="n">
-        <v>0.533</v>
+        <v>0.581</v>
       </c>
       <c r="G23" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="H23" t="n">
-        <v>51869.146</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>41.7</v>
+        <v>68172.103</v>
       </c>
       <c r="J23" t="n">
-        <v>1.71</v>
+        <v>83.3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CAE-lat32</t>
+          <t>DAE-lat64</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CAE</t>
+          <t>DAE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.717</v>
+        <v>64</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
       </c>
       <c r="E24" t="n">
-        <v>0.453</v>
+        <v>0.825</v>
       </c>
       <c r="F24" t="n">
-        <v>0.516</v>
+        <v>0.573</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="H24" t="n">
-        <v>228616.382</v>
+        <v>0.677</v>
       </c>
       <c r="I24" t="n">
-        <v>91.7</v>
+        <v>61639.768</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>83.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>224</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26896.349</v>
+      </c>
+      <c r="J25" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>160</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>34533.481</v>
+      </c>
+      <c r="J26" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>224</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I27" t="n">
+        <v>26436.608</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CAE-lat192</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>192</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="I28" t="n">
+        <v>26916.406</v>
+      </c>
+      <c r="J28" t="n">
+        <v>50</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CAE-lat192</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>192</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="I29" t="n">
+        <v>28694.199</v>
+      </c>
+      <c r="J29" t="n">
+        <v>50</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>CAE-lat64</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>64</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="I30" t="n">
+        <v>65289.497</v>
+      </c>
+      <c r="J30" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>CAE-lat64</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>64</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="I31" t="n">
+        <v>62822.284</v>
+      </c>
+      <c r="J31" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VAE-lat192</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>192</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="I32" t="n">
+        <v>27433.226</v>
+      </c>
+      <c r="J32" t="n">
+        <v>50</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VAE-lat192</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>192</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="I33" t="n">
+        <v>29229.916</v>
+      </c>
+      <c r="J33" t="n">
+        <v>50</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>32</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="I34" t="n">
+        <v>97861.56600000001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K34" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>32</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="I35" t="n">
+        <v>102704.634</v>
+      </c>
+      <c r="J35" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VAE-lat160</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>160</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="I36" t="n">
+        <v>31663.155</v>
+      </c>
+      <c r="J36" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VAE-lat224</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>224</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="I37" t="n">
+        <v>23956.915</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CAE-lat32</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>32</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="I38" t="n">
+        <v>111359.753</v>
+      </c>
+      <c r="J38" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K38" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VAE-lat160</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>160</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I39" t="n">
+        <v>32809.075</v>
+      </c>
+      <c r="J39" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VAE-lat224</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>224</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.747</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="I40" t="n">
+        <v>25930.115</v>
+      </c>
+      <c r="J40" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CAE-lat32</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CAE</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>32</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="I41" t="n">
+        <v>105967.53</v>
+      </c>
+      <c r="J41" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="K41" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>VAE-lat96</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>VAE</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C42" t="n">
         <v>96</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.671</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="H25" t="n">
-        <v>103594.345</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="I42" t="n">
+        <v>47853.458</v>
+      </c>
+      <c r="J42" t="n">
         <v>75</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K42" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VAE-lat96</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>VAE</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>96</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="I43" t="n">
+        <v>49969.311</v>
+      </c>
+      <c r="J43" t="n">
+        <v>75</v>
+      </c>
+      <c r="K43" t="n">
         <v>4</v>
       </c>
     </row>
